--- a/data_group/emmeans_intervalos_temp_table_final.xlsx
+++ b/data_group/emmeans_intervalos_temp_table_final.xlsx
@@ -458,31 +458,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>26.0458158846612</v>
+        <v>26.0469073100349</v>
       </c>
       <c r="D2" t="n">
-        <v>25.5475209067752</v>
+        <v>25.5484700515888</v>
       </c>
       <c r="E2" t="n">
-        <v>25.2666616138707</v>
+        <v>25.2695134640719</v>
       </c>
       <c r="F2" t="n">
-        <v>25.8867193203397</v>
+        <v>26.0165991771096</v>
       </c>
       <c r="G2" t="n">
-        <v>25.3976142570803</v>
+        <v>25.4854439292624</v>
       </c>
       <c r="H2" t="n">
-        <v>25.0947300144698</v>
+        <v>25.2459479508002</v>
       </c>
       <c r="I2" t="n">
-        <v>26.2049124489826</v>
+        <v>26.0772154429602</v>
       </c>
       <c r="J2" t="n">
-        <v>25.6974275564701</v>
+        <v>25.6114961739151</v>
       </c>
       <c r="K2" t="n">
-        <v>25.4385932132716</v>
+        <v>25.2930789773437</v>
       </c>
     </row>
     <row r="3">
@@ -493,31 +493,31 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>25.8849220382411</v>
+        <v>25.8806071230423</v>
       </c>
       <c r="D3" t="n">
-        <v>25.8588636400146</v>
+        <v>25.8560728830227</v>
       </c>
       <c r="E3" t="n">
-        <v>25.8546238434838</v>
+        <v>25.8644534097431</v>
       </c>
       <c r="F3" t="n">
-        <v>25.725825473914</v>
+        <v>25.842024778748</v>
       </c>
       <c r="G3" t="n">
-        <v>25.708956990322</v>
+        <v>25.8405852145825</v>
       </c>
       <c r="H3" t="n">
-        <v>25.6826922440894</v>
+        <v>25.8262652557719</v>
       </c>
       <c r="I3" t="n">
-        <v>26.0440186025682</v>
+        <v>25.9191894673365</v>
       </c>
       <c r="J3" t="n">
-        <v>26.0087702897072</v>
+        <v>25.8715605514629</v>
       </c>
       <c r="K3" t="n">
-        <v>26.0265554428782</v>
+        <v>25.9026415637142</v>
       </c>
     </row>
     <row r="4">
@@ -528,31 +528,31 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>25.847198168866</v>
+        <v>25.8477178505201</v>
       </c>
       <c r="D4" t="n">
-        <v>25.8557396450652</v>
+        <v>25.8524812355983</v>
       </c>
       <c r="E4" t="n">
-        <v>25.8122505515455</v>
+        <v>25.8565845659503</v>
       </c>
       <c r="F4" t="n">
-        <v>25.688101604539</v>
+        <v>25.8179464774112</v>
       </c>
       <c r="G4" t="n">
-        <v>25.7058329953726</v>
+        <v>25.8287670662411</v>
       </c>
       <c r="H4" t="n">
-        <v>25.6403189521511</v>
+        <v>25.80511950497</v>
       </c>
       <c r="I4" t="n">
-        <v>26.006294733193</v>
+        <v>25.8774892236289</v>
       </c>
       <c r="J4" t="n">
-        <v>26.0056462947578</v>
+        <v>25.8761954049556</v>
       </c>
       <c r="K4" t="n">
-        <v>25.9841821509399</v>
+        <v>25.9080496269307</v>
       </c>
     </row>
     <row r="5">
@@ -563,31 +563,31 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>25.878819885987</v>
+        <v>25.8530913114028</v>
       </c>
       <c r="D5" t="n">
-        <v>25.8866360238909</v>
+        <v>25.869427342237</v>
       </c>
       <c r="E5" t="n">
-        <v>25.7741657132707</v>
+        <v>25.8011782437645</v>
       </c>
       <c r="F5" t="n">
-        <v>25.7147184672271</v>
+        <v>25.8165633022046</v>
       </c>
       <c r="G5" t="n">
-        <v>25.7352301814158</v>
+        <v>25.844381615991</v>
       </c>
       <c r="H5" t="n">
-        <v>25.6001474613773</v>
+        <v>25.7580472603698</v>
       </c>
       <c r="I5" t="n">
-        <v>26.0429213047468</v>
+        <v>25.889619320601</v>
       </c>
       <c r="J5" t="n">
-        <v>26.038041866366</v>
+        <v>25.8944730684831</v>
       </c>
       <c r="K5" t="n">
-        <v>25.9481839651641</v>
+        <v>25.8443092271591</v>
       </c>
     </row>
     <row r="6">
@@ -598,31 +598,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>25.8257692242717</v>
+        <v>25.8264542628721</v>
       </c>
       <c r="D6" t="n">
-        <v>25.3932856909706</v>
+        <v>25.3935918835044</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1888473858282</v>
+        <v>25.1904139692511</v>
       </c>
       <c r="F6" t="n">
-        <v>25.6666726599505</v>
+        <v>25.8028168039263</v>
       </c>
       <c r="G6" t="n">
-        <v>25.243379041276</v>
+        <v>25.338077234332</v>
       </c>
       <c r="H6" t="n">
-        <v>25.0169157864286</v>
+        <v>25.1715697502923</v>
       </c>
       <c r="I6" t="n">
-        <v>25.9848657885929</v>
+        <v>25.8500917218178</v>
       </c>
       <c r="J6" t="n">
-        <v>25.5431923406652</v>
+        <v>25.4491065326767</v>
       </c>
       <c r="K6" t="n">
-        <v>25.3607789852278</v>
+        <v>25.2092581882098</v>
       </c>
     </row>
     <row r="7">
@@ -633,31 +633,31 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>25.8248583682045</v>
+        <v>25.8183528156668</v>
       </c>
       <c r="D7" t="n">
-        <v>25.7692490013997</v>
+        <v>25.7685919804562</v>
       </c>
       <c r="E7" t="n">
-        <v>25.6415639103494</v>
+        <v>25.6529155846636</v>
       </c>
       <c r="F7" t="n">
-        <v>25.6657618038773</v>
+        <v>25.7723063985093</v>
       </c>
       <c r="G7" t="n">
-        <v>25.619342351707</v>
+        <v>25.7608893818151</v>
       </c>
       <c r="H7" t="n">
-        <v>25.4696323109551</v>
+        <v>25.6256093436861</v>
       </c>
       <c r="I7" t="n">
-        <v>25.9839549325318</v>
+        <v>25.8643992328243</v>
       </c>
       <c r="J7" t="n">
-        <v>25.9191556510925</v>
+        <v>25.7762945790974</v>
       </c>
       <c r="K7" t="n">
-        <v>25.8134955097437</v>
+        <v>25.6802218256411</v>
       </c>
     </row>
     <row r="8">
@@ -668,31 +668,31 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>25.8688923260461</v>
+        <v>25.871430503136</v>
       </c>
       <c r="D8" t="n">
-        <v>25.789924557819</v>
+        <v>25.7762202614944</v>
       </c>
       <c r="E8" t="n">
-        <v>25.7224960134234</v>
+        <v>25.7611256246855</v>
       </c>
       <c r="F8" t="n">
-        <v>25.7097957617189</v>
+        <v>25.8363325724704</v>
       </c>
       <c r="G8" t="n">
-        <v>25.6400179081262</v>
+        <v>25.7572568772019</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5505644140291</v>
+        <v>25.708629260761</v>
       </c>
       <c r="I8" t="n">
-        <v>26.0279888903732</v>
+        <v>25.9065284338017</v>
       </c>
       <c r="J8" t="n">
-        <v>25.9398312075118</v>
+        <v>25.795183645787</v>
       </c>
       <c r="K8" t="n">
-        <v>25.8944276128178</v>
+        <v>25.81362198861</v>
       </c>
     </row>
     <row r="9">
@@ -703,31 +703,31 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>25.9404057871422</v>
+        <v>25.922339499777</v>
       </c>
       <c r="D9" t="n">
-        <v>25.7961079631741</v>
+        <v>25.7859258260335</v>
       </c>
       <c r="E9" t="n">
-        <v>25.7222825272642</v>
+        <v>25.7586578127168</v>
       </c>
       <c r="F9" t="n">
-        <v>25.7763043683823</v>
+        <v>25.8857213970472</v>
       </c>
       <c r="G9" t="n">
-        <v>25.6447021206989</v>
+        <v>25.7711910214292</v>
       </c>
       <c r="H9" t="n">
-        <v>25.5482642753708</v>
+        <v>25.7136744734997</v>
       </c>
       <c r="I9" t="n">
-        <v>26.1045072059022</v>
+        <v>25.9589576025068</v>
       </c>
       <c r="J9" t="n">
-        <v>25.9475138056494</v>
+        <v>25.8006606306378</v>
       </c>
       <c r="K9" t="n">
-        <v>25.8963007791576</v>
+        <v>25.803641151934</v>
       </c>
     </row>
     <row r="10">
@@ -738,31 +738,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>25.687787517344</v>
+        <v>25.6880228169644</v>
       </c>
       <c r="D10" t="n">
-        <v>25.3260144215824</v>
+        <v>25.3254979386633</v>
       </c>
       <c r="E10" t="n">
-        <v>25.1220395728907</v>
+        <v>25.1224071065132</v>
       </c>
       <c r="F10" t="n">
-        <v>25.528690953023</v>
+        <v>25.6728689950933</v>
       </c>
       <c r="G10" t="n">
-        <v>25.1761077718879</v>
+        <v>25.2755918008978</v>
       </c>
       <c r="H10" t="n">
-        <v>24.9501079734914</v>
+        <v>25.1107965863931</v>
       </c>
       <c r="I10" t="n">
-        <v>25.8468840816649</v>
+        <v>25.7031766388355</v>
       </c>
       <c r="J10" t="n">
-        <v>25.4759210712769</v>
+        <v>25.3754040764288</v>
       </c>
       <c r="K10" t="n">
-        <v>25.2939711722901</v>
+        <v>25.1340176266333</v>
       </c>
     </row>
     <row r="11">
@@ -773,31 +773,31 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>25.7890829467623</v>
+        <v>25.7854666261676</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7254806969353</v>
+        <v>25.7236306540672</v>
       </c>
       <c r="E11" t="n">
-        <v>25.4658267477683</v>
+        <v>25.4665403550656</v>
       </c>
       <c r="F11" t="n">
-        <v>25.6299863824351</v>
+        <v>25.731997140293</v>
       </c>
       <c r="G11" t="n">
-        <v>25.5755740472426</v>
+        <v>25.7074836165865</v>
       </c>
       <c r="H11" t="n">
-        <v>25.2938951483738</v>
+        <v>25.4418619346876</v>
       </c>
       <c r="I11" t="n">
-        <v>25.9481795110895</v>
+        <v>25.8389361120422</v>
       </c>
       <c r="J11" t="n">
-        <v>25.875387346628</v>
+        <v>25.739777691548</v>
       </c>
       <c r="K11" t="n">
-        <v>25.6377583471628</v>
+        <v>25.4912187754435</v>
       </c>
     </row>
     <row r="12">
@@ -808,31 +808,31 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>25.8400210257285</v>
+        <v>25.8460036839263</v>
       </c>
       <c r="D12" t="n">
-        <v>25.7376365950127</v>
+        <v>25.716781015446</v>
       </c>
       <c r="E12" t="n">
-        <v>25.6267018319839</v>
+        <v>25.6564388612986</v>
       </c>
       <c r="F12" t="n">
-        <v>25.6809244614014</v>
+        <v>25.8068621529291</v>
       </c>
       <c r="G12" t="n">
-        <v>25.58772994532</v>
+        <v>25.6970388128405</v>
       </c>
       <c r="H12" t="n">
-        <v>25.4547702325895</v>
+        <v>25.602657640396</v>
       </c>
       <c r="I12" t="n">
-        <v>25.9991175900556</v>
+        <v>25.8851452149235</v>
       </c>
       <c r="J12" t="n">
-        <v>25.8875432447054</v>
+        <v>25.7365232180515</v>
       </c>
       <c r="K12" t="n">
-        <v>25.7986334313784</v>
+        <v>25.7102200822012</v>
       </c>
     </row>
     <row r="13">
@@ -843,31 +843,31 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>25.9203680688124</v>
+        <v>25.9101891735948</v>
       </c>
       <c r="D13" t="n">
-        <v>25.7022961927397</v>
+        <v>25.6962308557908</v>
       </c>
       <c r="E13" t="n">
-        <v>25.6071877906521</v>
+        <v>25.6479359504949</v>
       </c>
       <c r="F13" t="n">
-        <v>25.7562666500526</v>
+        <v>25.8691385329373</v>
       </c>
       <c r="G13" t="n">
-        <v>25.5508903502646</v>
+        <v>25.6852227009794</v>
       </c>
       <c r="H13" t="n">
-        <v>25.4331695387586</v>
+        <v>25.6058802857183</v>
       </c>
       <c r="I13" t="n">
-        <v>26.0844694875723</v>
+        <v>25.9512398142522</v>
       </c>
       <c r="J13" t="n">
-        <v>25.8537020352149</v>
+        <v>25.7072390106021</v>
       </c>
       <c r="K13" t="n">
-        <v>25.7812060425457</v>
+        <v>25.6899916152716</v>
       </c>
     </row>
     <row r="14">
@@ -878,31 +878,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>25.6016919253991</v>
+        <v>25.6017031298139</v>
       </c>
       <c r="D14" t="n">
-        <v>25.3032882487166</v>
+        <v>25.3021480779094</v>
       </c>
       <c r="E14" t="n">
-        <v>25.0865904666814</v>
+        <v>25.0866382918527</v>
       </c>
       <c r="F14" t="n">
-        <v>25.4425953610784</v>
+        <v>25.5921136898375</v>
       </c>
       <c r="G14" t="n">
-        <v>25.1533815990223</v>
+        <v>25.2606437620018</v>
       </c>
       <c r="H14" t="n">
-        <v>24.9146588672818</v>
+        <v>25.0784732281398</v>
       </c>
       <c r="I14" t="n">
-        <v>25.7607884897198</v>
+        <v>25.6112925697903</v>
       </c>
       <c r="J14" t="n">
-        <v>25.4531948984109</v>
+        <v>25.343652393817</v>
       </c>
       <c r="K14" t="n">
-        <v>25.2585220660811</v>
+        <v>25.0948033555655</v>
       </c>
     </row>
     <row r="15">
@@ -913,31 +913,31 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>25.6894984825401</v>
+        <v>25.6890978813705</v>
       </c>
       <c r="D15" t="n">
-        <v>25.6729195767872</v>
+        <v>25.6680187598825</v>
       </c>
       <c r="E15" t="n">
-        <v>25.3145522691824</v>
+        <v>25.3051497385154</v>
       </c>
       <c r="F15" t="n">
-        <v>25.5304019182128</v>
+        <v>25.6291610230566</v>
       </c>
       <c r="G15" t="n">
-        <v>25.5230129270947</v>
+        <v>25.6457190898283</v>
       </c>
       <c r="H15" t="n">
-        <v>25.1426206697877</v>
+        <v>25.2768455282612</v>
       </c>
       <c r="I15" t="n">
-        <v>25.8485950468674</v>
+        <v>25.7490347396844</v>
       </c>
       <c r="J15" t="n">
-        <v>25.8228262264797</v>
+        <v>25.6903184299367</v>
       </c>
       <c r="K15" t="n">
-        <v>25.4864838685771</v>
+        <v>25.3334539487697</v>
       </c>
     </row>
     <row r="16">
@@ -948,31 +948,31 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>25.7879563582102</v>
+        <v>25.7997480657604</v>
       </c>
       <c r="D16" t="n">
-        <v>25.6976990363773</v>
+        <v>25.6761676311224</v>
       </c>
       <c r="E16" t="n">
-        <v>25.5023091684757</v>
+        <v>25.516589590925</v>
       </c>
       <c r="F16" t="n">
-        <v>25.628859793883</v>
+        <v>25.7551296778127</v>
       </c>
       <c r="G16" t="n">
-        <v>25.5477923866847</v>
+        <v>25.6560858271909</v>
       </c>
       <c r="H16" t="n">
-        <v>25.330377569081</v>
+        <v>25.4675169103274</v>
       </c>
       <c r="I16" t="n">
-        <v>25.9470529225374</v>
+        <v>25.844366453708</v>
       </c>
       <c r="J16" t="n">
-        <v>25.8476056860698</v>
+        <v>25.696249435054</v>
       </c>
       <c r="K16" t="n">
-        <v>25.6742407678704</v>
+        <v>25.5656622715226</v>
       </c>
     </row>
     <row r="17">
@@ -983,31 +983,31 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>25.8957080153011</v>
+        <v>25.8828011987853</v>
       </c>
       <c r="D17" t="n">
-        <v>25.6573412573726</v>
+        <v>25.6511550708072</v>
       </c>
       <c r="E17" t="n">
-        <v>25.5182643300475</v>
+        <v>25.5568546294306</v>
       </c>
       <c r="F17" t="n">
-        <v>25.731606596541</v>
+        <v>25.8350620904718</v>
       </c>
       <c r="G17" t="n">
-        <v>25.5059354148977</v>
+        <v>25.6406689633672</v>
       </c>
       <c r="H17" t="n">
-        <v>25.3442460781537</v>
+        <v>25.5148215160707</v>
       </c>
       <c r="I17" t="n">
-        <v>26.0598094340611</v>
+        <v>25.9305403070989</v>
       </c>
       <c r="J17" t="n">
-        <v>25.8087470998476</v>
+        <v>25.6616411782473</v>
       </c>
       <c r="K17" t="n">
-        <v>25.6922825819412</v>
+        <v>25.5988877427906</v>
       </c>
     </row>
     <row r="18">
@@ -1018,31 +1018,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>25.5387112720047</v>
+        <v>25.5386854204973</v>
       </c>
       <c r="D18" t="n">
-        <v>25.3472173432427</v>
+        <v>25.3463452332252</v>
       </c>
       <c r="E18" t="n">
-        <v>25.1876041122628</v>
+        <v>25.1888436819644</v>
       </c>
       <c r="F18" t="n">
-        <v>25.379614707684</v>
+        <v>25.5335540055492</v>
       </c>
       <c r="G18" t="n">
-        <v>25.1973106935482</v>
+        <v>25.3115115596778</v>
       </c>
       <c r="H18" t="n">
-        <v>25.0156725128629</v>
+        <v>25.1796924628473</v>
       </c>
       <c r="I18" t="n">
-        <v>25.6978078363254</v>
+        <v>25.5438168354454</v>
       </c>
       <c r="J18" t="n">
-        <v>25.4971239929372</v>
+        <v>25.3811789067725</v>
       </c>
       <c r="K18" t="n">
-        <v>25.3595357116627</v>
+        <v>25.1979949010815</v>
       </c>
     </row>
     <row r="19">
@@ -1053,31 +1053,31 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>25.6485258381895</v>
+        <v>25.6478216334423</v>
       </c>
       <c r="D19" t="n">
-        <v>25.615047861782</v>
+        <v>25.6061234765377</v>
       </c>
       <c r="E19" t="n">
-        <v>25.225638782726</v>
+        <v>25.2188730692113</v>
       </c>
       <c r="F19" t="n">
-        <v>25.4894292738622</v>
+        <v>25.5853677044927</v>
       </c>
       <c r="G19" t="n">
-        <v>25.4651412120894</v>
+        <v>25.5824602463549</v>
       </c>
       <c r="H19" t="n">
-        <v>25.0537071833315</v>
+        <v>25.1922341687488</v>
       </c>
       <c r="I19" t="n">
-        <v>25.8076224025168</v>
+        <v>25.7102755623919</v>
       </c>
       <c r="J19" t="n">
-        <v>25.7649545114746</v>
+        <v>25.6297867067206</v>
       </c>
       <c r="K19" t="n">
-        <v>25.3975703821205</v>
+        <v>25.2455119696738</v>
       </c>
     </row>
     <row r="20">
@@ -1088,31 +1088,31 @@
         <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>25.7467739879847</v>
+        <v>25.7496870425416</v>
       </c>
       <c r="D20" t="n">
-        <v>25.6541377792689</v>
+        <v>25.6344747910357</v>
       </c>
       <c r="E20" t="n">
-        <v>25.3913651086338</v>
+        <v>25.3978989543721</v>
       </c>
       <c r="F20" t="n">
-        <v>25.5876774236575</v>
+        <v>25.703688065826</v>
       </c>
       <c r="G20" t="n">
-        <v>25.5042311295763</v>
+        <v>25.6142188000324</v>
       </c>
       <c r="H20" t="n">
-        <v>25.2194335092393</v>
+        <v>25.3620084231861</v>
       </c>
       <c r="I20" t="n">
-        <v>25.9058705523118</v>
+        <v>25.7956860192571</v>
       </c>
       <c r="J20" t="n">
-        <v>25.8040444289615</v>
+        <v>25.6547307820389</v>
       </c>
       <c r="K20" t="n">
-        <v>25.5632967080284</v>
+        <v>25.4337894855582</v>
       </c>
     </row>
     <row r="21">
@@ -1123,31 +1123,31 @@
         <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>25.8580683069251</v>
+        <v>25.8534855912485</v>
       </c>
       <c r="D21" t="n">
-        <v>25.6194295767751</v>
+        <v>25.6033637200628</v>
       </c>
       <c r="E21" t="n">
-        <v>25.4174390374064</v>
+        <v>25.4640183725181</v>
       </c>
       <c r="F21" t="n">
-        <v>25.6939668881652</v>
+        <v>25.8051732470767</v>
       </c>
       <c r="G21" t="n">
-        <v>25.4680237343</v>
+        <v>25.592813551162</v>
       </c>
       <c r="H21" t="n">
-        <v>25.2434207855129</v>
+        <v>25.4135542843997</v>
       </c>
       <c r="I21" t="n">
-        <v>26.0221697256851</v>
+        <v>25.9017979354203</v>
       </c>
       <c r="J21" t="n">
-        <v>25.7708354192501</v>
+        <v>25.6139138889637</v>
       </c>
       <c r="K21" t="n">
-        <v>25.5914572893</v>
+        <v>25.5144824606364</v>
       </c>
     </row>
     <row r="22">
@@ -1158,31 +1158,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>25.5091687622036</v>
+        <v>25.5092080361776</v>
       </c>
       <c r="D22" t="n">
-        <v>25.3591294457079</v>
+        <v>25.3598378619062</v>
       </c>
       <c r="E22" t="n">
-        <v>25.2855496288246</v>
+        <v>25.2857339590974</v>
       </c>
       <c r="F22" t="n">
-        <v>25.3500721978828</v>
+        <v>25.5061538847816</v>
       </c>
       <c r="G22" t="n">
-        <v>25.2092227960134</v>
+        <v>25.3260374290775</v>
       </c>
       <c r="H22" t="n">
-        <v>25.1136180294242</v>
+        <v>25.2796070103359</v>
       </c>
       <c r="I22" t="n">
-        <v>25.6682653265244</v>
+        <v>25.5122621875737</v>
       </c>
       <c r="J22" t="n">
-        <v>25.5090360954024</v>
+        <v>25.393638294735</v>
       </c>
       <c r="K22" t="n">
-        <v>25.457481228225</v>
+        <v>25.2918609078589</v>
       </c>
     </row>
     <row r="23">
@@ -1193,31 +1193,31 @@
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>25.6664819944231</v>
+        <v>25.6688497781346</v>
       </c>
       <c r="D23" t="n">
-        <v>25.5934838073841</v>
+        <v>25.5821778303766</v>
       </c>
       <c r="E23" t="n">
-        <v>25.1139831340761</v>
+        <v>25.0809846473651</v>
       </c>
       <c r="F23" t="n">
-        <v>25.5073854300959</v>
+        <v>25.554408706202</v>
       </c>
       <c r="G23" t="n">
-        <v>25.4435771576916</v>
+        <v>25.552211921335</v>
       </c>
       <c r="H23" t="n">
-        <v>24.9420515346816</v>
+        <v>25.0470072700809</v>
       </c>
       <c r="I23" t="n">
-        <v>25.8255785587503</v>
+        <v>25.7832908500671</v>
       </c>
       <c r="J23" t="n">
-        <v>25.7433904570766</v>
+        <v>25.6121437394183</v>
       </c>
       <c r="K23" t="n">
-        <v>25.2859147334706</v>
+        <v>25.1149620246493</v>
       </c>
     </row>
     <row r="24">
@@ -1228,31 +1228,31 @@
         <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>25.6707912997987</v>
+        <v>25.6757360383977</v>
       </c>
       <c r="D24" t="n">
-        <v>25.615824000115</v>
+        <v>25.5917153562024</v>
       </c>
       <c r="E24" t="n">
-        <v>25.3405917173887</v>
+        <v>25.3290867758411</v>
       </c>
       <c r="F24" t="n">
-        <v>25.5116947354717</v>
+        <v>25.6310672661518</v>
       </c>
       <c r="G24" t="n">
-        <v>25.4659173504225</v>
+        <v>25.5678124191535</v>
       </c>
       <c r="H24" t="n">
-        <v>25.1686601179941</v>
+        <v>25.2901177771477</v>
       </c>
       <c r="I24" t="n">
-        <v>25.8298878641258</v>
+        <v>25.7204048106437</v>
       </c>
       <c r="J24" t="n">
-        <v>25.7657306498075</v>
+        <v>25.6156182932512</v>
       </c>
       <c r="K24" t="n">
-        <v>25.5125233167832</v>
+        <v>25.3680557745345</v>
       </c>
     </row>
     <row r="25">
@@ -1263,31 +1263,31 @@
         <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>25.7673902414027</v>
+        <v>25.7650894686512</v>
       </c>
       <c r="D25" t="n">
-        <v>25.5901537634747</v>
+        <v>25.5747905227714</v>
       </c>
       <c r="E25" t="n">
-        <v>25.345256603849</v>
+        <v>25.3826956986025</v>
       </c>
       <c r="F25" t="n">
-        <v>25.6032888226429</v>
+        <v>25.7125255395633</v>
       </c>
       <c r="G25" t="n">
-        <v>25.4387479209998</v>
+        <v>25.5611268553598</v>
       </c>
       <c r="H25" t="n">
-        <v>25.1712383519554</v>
+        <v>25.3367841131847</v>
       </c>
       <c r="I25" t="n">
-        <v>25.9314916601626</v>
+        <v>25.8176533977391</v>
       </c>
       <c r="J25" t="n">
-        <v>25.7415596059497</v>
+        <v>25.5884541901831</v>
       </c>
       <c r="K25" t="n">
-        <v>25.5192748557425</v>
+        <v>25.4286072840203</v>
       </c>
     </row>
     <row r="26">
@@ -1298,31 +1298,31 @@
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>25.4420803765872</v>
+        <v>25.4420803770376</v>
       </c>
       <c r="D26" t="n">
-        <v>25.2468379049576</v>
+        <v>25.2494981274987</v>
       </c>
       <c r="E26" t="n">
-        <v>25.16945815293</v>
+        <v>25.16956287215</v>
       </c>
       <c r="F26" t="n">
-        <v>25.2829838122664</v>
+        <v>25.4420730242666</v>
       </c>
       <c r="G26" t="n">
-        <v>25.0969312552628</v>
+        <v>25.2127909307552</v>
       </c>
       <c r="H26" t="n">
-        <v>24.9975265535296</v>
+        <v>25.1638444438111</v>
       </c>
       <c r="I26" t="n">
-        <v>25.6011769409081</v>
+        <v>25.4420877298085</v>
       </c>
       <c r="J26" t="n">
-        <v>25.3967445546523</v>
+        <v>25.2862053242421</v>
       </c>
       <c r="K26" t="n">
-        <v>25.3413897523303</v>
+        <v>25.175281300489</v>
       </c>
     </row>
     <row r="27">
@@ -1333,31 +1333,31 @@
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>25.6369157657588</v>
+        <v>25.6483129049768</v>
       </c>
       <c r="D27" t="n">
-        <v>25.528937059959</v>
+        <v>25.5189894215787</v>
       </c>
       <c r="E27" t="n">
-        <v>25.0391313463755</v>
+        <v>24.9826341852972</v>
       </c>
       <c r="F27" t="n">
-        <v>25.4778192014315</v>
+        <v>25.5558629924424</v>
       </c>
       <c r="G27" t="n">
-        <v>25.3790304102665</v>
+        <v>25.489522300394</v>
       </c>
       <c r="H27" t="n">
-        <v>24.8671997469808</v>
+        <v>24.9363145167078</v>
       </c>
       <c r="I27" t="n">
-        <v>25.796012330086</v>
+        <v>25.7407628175111</v>
       </c>
       <c r="J27" t="n">
-        <v>25.6788437096516</v>
+        <v>25.5484565427634</v>
       </c>
       <c r="K27" t="n">
-        <v>25.2110629457703</v>
+        <v>25.0289538538866</v>
       </c>
     </row>
     <row r="28">
@@ -1368,31 +1368,31 @@
         <v>14</v>
       </c>
       <c r="C28" t="n">
-        <v>25.5965954367584</v>
+        <v>25.6112539121166</v>
       </c>
       <c r="D28" t="n">
-        <v>25.5471115440873</v>
+        <v>25.5276734070192</v>
       </c>
       <c r="E28" t="n">
-        <v>25.2175540697929</v>
+        <v>25.213071187149</v>
       </c>
       <c r="F28" t="n">
-        <v>25.4374988724312</v>
+        <v>25.5642765305122</v>
       </c>
       <c r="G28" t="n">
-        <v>25.3972048943947</v>
+        <v>25.5019957240599</v>
       </c>
       <c r="H28" t="n">
-        <v>25.0456224703982</v>
+        <v>25.162338066402</v>
       </c>
       <c r="I28" t="n">
-        <v>25.7556920010855</v>
+        <v>25.6582312937209</v>
       </c>
       <c r="J28" t="n">
-        <v>25.6970181937799</v>
+        <v>25.5533510899785</v>
       </c>
       <c r="K28" t="n">
-        <v>25.3894856691876</v>
+        <v>25.263804307896</v>
       </c>
     </row>
     <row r="29">
@@ -1403,31 +1403,31 @@
         <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>25.7005855076344</v>
+        <v>25.6873702407074</v>
       </c>
       <c r="D29" t="n">
-        <v>25.5278355465639</v>
+        <v>25.5134788862612</v>
       </c>
       <c r="E29" t="n">
-        <v>25.2405148616061</v>
+        <v>25.3043130157942</v>
       </c>
       <c r="F29" t="n">
-        <v>25.5364840888744</v>
+        <v>25.6428552289712</v>
       </c>
       <c r="G29" t="n">
-        <v>25.3764297040888</v>
+        <v>25.4989538691015</v>
       </c>
       <c r="H29" t="n">
-        <v>25.0664966097123</v>
+        <v>25.2329185689726</v>
       </c>
       <c r="I29" t="n">
-        <v>25.8646869263943</v>
+        <v>25.7318852524437</v>
       </c>
       <c r="J29" t="n">
-        <v>25.6792413890389</v>
+        <v>25.5280039034208</v>
       </c>
       <c r="K29" t="n">
-        <v>25.4145331134998</v>
+        <v>25.3757074626159</v>
       </c>
     </row>
     <row r="30">
@@ -1438,31 +1438,31 @@
         <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>25.3753185662265</v>
+        <v>25.3753206788826</v>
       </c>
       <c r="D30" t="n">
-        <v>25.1309643853327</v>
+        <v>25.1356359798866</v>
       </c>
       <c r="E30" t="n">
-        <v>25.0597774471671</v>
+        <v>25.0601275882654</v>
       </c>
       <c r="F30" t="n">
-        <v>25.2162220019055</v>
+        <v>25.3731423483024</v>
       </c>
       <c r="G30" t="n">
-        <v>24.9810577356384</v>
+        <v>25.0961245998871</v>
       </c>
       <c r="H30" t="n">
-        <v>24.8878458477672</v>
+        <v>25.0517180627234</v>
       </c>
       <c r="I30" t="n">
-        <v>25.5344151305476</v>
+        <v>25.3774990094628</v>
       </c>
       <c r="J30" t="n">
-        <v>25.2808710350271</v>
+        <v>25.175147359886</v>
       </c>
       <c r="K30" t="n">
-        <v>25.2317090465669</v>
+        <v>25.0685371138075</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         <v>13</v>
       </c>
       <c r="C31" t="n">
-        <v>25.6382070591541</v>
+        <v>25.6107181323977</v>
       </c>
       <c r="D31" t="n">
-        <v>25.4774074641507</v>
+        <v>25.4713837621266</v>
       </c>
       <c r="E31" t="n">
-        <v>24.8925513212202</v>
+        <v>24.838453804175</v>
       </c>
       <c r="F31" t="n">
-        <v>25.4791104948268</v>
+        <v>25.481894529354</v>
       </c>
       <c r="G31" t="n">
-        <v>25.3275008144583</v>
+        <v>25.447358819484</v>
       </c>
       <c r="H31" t="n">
-        <v>24.7206197218258</v>
+        <v>24.7927677546532</v>
       </c>
       <c r="I31" t="n">
-        <v>25.7973036234813</v>
+        <v>25.7395417354415</v>
       </c>
       <c r="J31" t="n">
-        <v>25.6273141138432</v>
+        <v>25.4954087047693</v>
       </c>
       <c r="K31" t="n">
-        <v>25.0644829206146</v>
+        <v>24.8841398536969</v>
       </c>
     </row>
     <row r="32">
@@ -1508,31 +1508,31 @@
         <v>14</v>
       </c>
       <c r="C32" t="n">
-        <v>25.6453137864579</v>
+        <v>25.6384508443756</v>
       </c>
       <c r="D32" t="n">
-        <v>25.4902823730133</v>
+        <v>25.4703117284536</v>
       </c>
       <c r="E32" t="n">
-        <v>25.0877763991161</v>
+        <v>25.0729354620705</v>
       </c>
       <c r="F32" t="n">
-        <v>25.4862172221308</v>
+        <v>25.5774041750646</v>
       </c>
       <c r="G32" t="n">
-        <v>25.3403757233208</v>
+        <v>25.442307447981</v>
       </c>
       <c r="H32" t="n">
-        <v>24.9158447997217</v>
+        <v>25.0233508612641</v>
       </c>
       <c r="I32" t="n">
-        <v>25.804410350785</v>
+        <v>25.6994975136867</v>
       </c>
       <c r="J32" t="n">
-        <v>25.6401890227058</v>
+        <v>25.4983160089262</v>
       </c>
       <c r="K32" t="n">
-        <v>25.2597079985105</v>
+        <v>25.122520062877</v>
       </c>
     </row>
     <row r="33">
@@ -1543,31 +1543,31 @@
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>25.6559011189694</v>
+        <v>25.6617503711059</v>
       </c>
       <c r="D33" t="n">
-        <v>25.4468528589829</v>
+        <v>25.4347018454818</v>
       </c>
       <c r="E33" t="n">
-        <v>24.9372316622198</v>
+        <v>24.9678289330953</v>
       </c>
       <c r="F33" t="n">
-        <v>25.4917997002095</v>
+        <v>25.5940395383126</v>
       </c>
       <c r="G33" t="n">
-        <v>25.2954470165079</v>
+        <v>25.4185069257414</v>
       </c>
       <c r="H33" t="n">
-        <v>24.7632134103263</v>
+        <v>24.9222853858667</v>
       </c>
       <c r="I33" t="n">
-        <v>25.8200025377293</v>
+        <v>25.7294612038991</v>
       </c>
       <c r="J33" t="n">
-        <v>25.5982587014579</v>
+        <v>25.4508967652222</v>
       </c>
       <c r="K33" t="n">
-        <v>25.1112499141132</v>
+        <v>25.013372480324</v>
       </c>
     </row>
     <row r="34">
@@ -1578,31 +1578,31 @@
         <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>25.3154123157704</v>
+        <v>25.3153841169128</v>
       </c>
       <c r="D34" t="n">
-        <v>24.9950567614558</v>
+        <v>25.001458650452</v>
       </c>
       <c r="E34" t="n">
-        <v>24.9496740397818</v>
+        <v>24.9505375691259</v>
       </c>
       <c r="F34" t="n">
-        <v>25.1563157514494</v>
+        <v>25.3115543126219</v>
       </c>
       <c r="G34" t="n">
-        <v>24.8451501117613</v>
+        <v>24.9581508168376</v>
       </c>
       <c r="H34" t="n">
-        <v>24.7777424403823</v>
+        <v>24.9381678576915</v>
       </c>
       <c r="I34" t="n">
-        <v>25.4745088800914</v>
+        <v>25.3192139212038</v>
       </c>
       <c r="J34" t="n">
-        <v>25.1449634111504</v>
+        <v>25.0447664840664</v>
       </c>
       <c r="K34" t="n">
-        <v>25.1216056391813</v>
+        <v>24.9629072805602</v>
       </c>
     </row>
     <row r="35">
@@ -1613,31 +1613,31 @@
         <v>13</v>
       </c>
       <c r="C35" t="n">
-        <v>25.33995338074</v>
+        <v>25.3356216895818</v>
       </c>
       <c r="D35" t="n">
-        <v>25.4071053268214</v>
+        <v>25.3946994676728</v>
       </c>
       <c r="E35" t="n">
-        <v>24.8128489755132</v>
+        <v>24.7958303041163</v>
       </c>
       <c r="F35" t="n">
-        <v>25.1798054934128</v>
+        <v>25.1949527691581</v>
       </c>
       <c r="G35" t="n">
-        <v>25.2571986771289</v>
+        <v>25.3623407431555</v>
       </c>
       <c r="H35" t="n">
-        <v>24.6409173761187</v>
+        <v>24.7497182828446</v>
       </c>
       <c r="I35" t="n">
-        <v>25.5001012680672</v>
+        <v>25.4762906100055</v>
       </c>
       <c r="J35" t="n">
-        <v>25.5570119765138</v>
+        <v>25.4270581921901</v>
       </c>
       <c r="K35" t="n">
-        <v>24.9847805749076</v>
+        <v>24.8419423253881</v>
       </c>
     </row>
     <row r="36">
@@ -1648,31 +1648,31 @@
         <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>25.5230432737404</v>
+        <v>25.4617237864691</v>
       </c>
       <c r="D36" t="n">
-        <v>25.3688236916028</v>
+        <v>25.3467116298182</v>
       </c>
       <c r="E36" t="n">
-        <v>24.9482248347157</v>
+        <v>24.9549066130395</v>
       </c>
       <c r="F36" t="n">
-        <v>25.3639467094134</v>
+        <v>25.3947996516081</v>
       </c>
       <c r="G36" t="n">
-        <v>25.2189170419103</v>
+        <v>25.3170129577225</v>
       </c>
       <c r="H36" t="n">
-        <v>24.7762932353212</v>
+        <v>24.9227696953238</v>
       </c>
       <c r="I36" t="n">
-        <v>25.6821398380674</v>
+        <v>25.52864792133</v>
       </c>
       <c r="J36" t="n">
-        <v>25.5187303412953</v>
+        <v>25.3764103019138</v>
       </c>
       <c r="K36" t="n">
-        <v>25.1201564341101</v>
+        <v>24.9870435307553</v>
       </c>
     </row>
     <row r="37">
@@ -1683,31 +1683,31 @@
         <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>25.5840344189285</v>
+        <v>25.5697793912851</v>
       </c>
       <c r="D37" t="n">
-        <v>25.3344607139283</v>
+        <v>25.3221474926086</v>
       </c>
       <c r="E37" t="n">
-        <v>24.9227782555969</v>
+        <v>24.9391371398269</v>
       </c>
       <c r="F37" t="n">
-        <v>25.4199330001687</v>
+        <v>25.5117182434177</v>
       </c>
       <c r="G37" t="n">
-        <v>25.1830548714533</v>
+        <v>25.3032039450696</v>
       </c>
       <c r="H37" t="n">
-        <v>24.7487600037033</v>
+        <v>24.8917437705413</v>
       </c>
       <c r="I37" t="n">
-        <v>25.7481358376884</v>
+        <v>25.6278405391526</v>
       </c>
       <c r="J37" t="n">
-        <v>25.4858665564032</v>
+        <v>25.3410910401477</v>
       </c>
       <c r="K37" t="n">
-        <v>25.0967965074904</v>
+        <v>24.9865305091124</v>
       </c>
     </row>
     <row r="38">
@@ -1718,31 +1718,31 @@
         <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>24.9102935203089</v>
+        <v>24.9103563056581</v>
       </c>
       <c r="D38" t="n">
-        <v>24.5010569138636</v>
+        <v>24.5080709237316</v>
       </c>
       <c r="E38" t="n">
-        <v>24.5873165307819</v>
+        <v>24.5902344877997</v>
       </c>
       <c r="F38" t="n">
-        <v>24.7511969559885</v>
+        <v>24.896167848965</v>
       </c>
       <c r="G38" t="n">
-        <v>24.3511502641684</v>
+        <v>24.4542429110494</v>
       </c>
       <c r="H38" t="n">
-        <v>24.4153849313828</v>
+        <v>24.5601973217874</v>
       </c>
       <c r="I38" t="n">
-        <v>25.0693900846293</v>
+        <v>24.9245447623511</v>
       </c>
       <c r="J38" t="n">
-        <v>24.6509635635588</v>
+        <v>24.5618989364139</v>
       </c>
       <c r="K38" t="n">
-        <v>24.7592481301811</v>
+        <v>24.620271653812</v>
       </c>
     </row>
     <row r="39">
@@ -1753,31 +1753,31 @@
         <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>25.6081914133334</v>
+        <v>25.5314624062363</v>
       </c>
       <c r="D39" t="n">
-        <v>25.3175164041701</v>
+        <v>25.3435142600504</v>
       </c>
       <c r="E39" t="n">
-        <v>24.6565395452306</v>
+        <v>24.5443322348006</v>
       </c>
       <c r="F39" t="n">
-        <v>25.4451092877502</v>
+        <v>25.3898741779863</v>
       </c>
       <c r="G39" t="n">
-        <v>25.1676097544777</v>
+        <v>25.29567583877</v>
       </c>
       <c r="H39" t="n">
-        <v>24.4846079458362</v>
+        <v>24.4647278277895</v>
       </c>
       <c r="I39" t="n">
-        <v>25.7712735389167</v>
+        <v>25.6730506344864</v>
       </c>
       <c r="J39" t="n">
-        <v>25.4674230538626</v>
+        <v>25.3913526813308</v>
       </c>
       <c r="K39" t="n">
-        <v>24.828471144625</v>
+        <v>24.6239366418117</v>
       </c>
     </row>
     <row r="40">
@@ -1788,31 +1788,31 @@
         <v>14</v>
       </c>
       <c r="C40" t="n">
-        <v>25.4085253408478</v>
+        <v>25.3152982302995</v>
       </c>
       <c r="D40" t="n">
-        <v>25.2613302942671</v>
+        <v>25.2348650201871</v>
       </c>
       <c r="E40" t="n">
-        <v>24.7900194549429</v>
+        <v>24.7718578110971</v>
       </c>
       <c r="F40" t="n">
-        <v>25.2494287765207</v>
+        <v>25.1676977796729</v>
       </c>
       <c r="G40" t="n">
-        <v>25.1114236445747</v>
+        <v>25.2003349567853</v>
       </c>
       <c r="H40" t="n">
-        <v>24.6180878555484</v>
+        <v>24.7407751349691</v>
       </c>
       <c r="I40" t="n">
-        <v>25.5676219051749</v>
+        <v>25.462898680926</v>
       </c>
       <c r="J40" t="n">
-        <v>25.4112369439596</v>
+        <v>25.2693950835889</v>
       </c>
       <c r="K40" t="n">
-        <v>24.9619510543373</v>
+        <v>24.8029404872252</v>
       </c>
     </row>
     <row r="41">
@@ -1823,31 +1823,31 @@
         <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>25.2991119854602</v>
+        <v>25.263583511867</v>
       </c>
       <c r="D41" t="n">
-        <v>25.1690251054195</v>
+        <v>25.1711775587113</v>
       </c>
       <c r="E41" t="n">
-        <v>24.6274810218104</v>
+        <v>24.632734018645</v>
       </c>
       <c r="F41" t="n">
-        <v>25.1350105667003</v>
+        <v>25.2043935415709</v>
       </c>
       <c r="G41" t="n">
-        <v>25.0176192629446</v>
+        <v>25.1484256431561</v>
       </c>
       <c r="H41" t="n">
-        <v>24.453462769917</v>
+        <v>24.5960700441803</v>
       </c>
       <c r="I41" t="n">
-        <v>25.4632134042201</v>
+        <v>25.3227734821631</v>
       </c>
       <c r="J41" t="n">
-        <v>25.3204309478945</v>
+        <v>25.1939294742664</v>
       </c>
       <c r="K41" t="n">
-        <v>24.8014992737039</v>
+        <v>24.6693979931097</v>
       </c>
     </row>
   </sheetData>
